--- a/data/trans_orig/IP22D6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Edad-trans_orig.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96615</t>
+          <t>96787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6261</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10051</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7028</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12018</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9653</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12537</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8669</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5193</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9256</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6541</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1745,107 +1745,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4314</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,64 +2088,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19721</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17756</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,74 +2544,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>46065</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>47328</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>44171</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>42157</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>39330</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>52753</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>50370</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>53272</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -2619,27 +2619,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100081</t>
+          <t>90207</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96787</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2770,107 +2770,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
